--- a/data/trans_orig/IP16A112_2023R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A112_2023R-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23496</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20102</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15769</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31609</t>
+          <t>30842</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42647</t>
+          <t>42680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,45%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24131</t>
+          <t>24549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36805</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37656</t>
+          <t>36753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>56884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>20233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34568</t>
+          <t>33441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27004</t>
+          <t>27659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41154</t>
+          <t>41919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51874</t>
+          <t>51707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70935</t>
+          <t>71838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47553</t>
+          <t>48174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>19199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34235</t>
+          <t>34248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74495</t>
+          <t>74195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29518</t>
+          <t>28897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66914</t>
+          <t>67168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38163</t>
+          <t>37724</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59499</t>
+          <t>59799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102488</t>
+          <t>106431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21310</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>23542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37553</t>
+          <t>37348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26817</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40322</t>
+          <t>40828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>44851</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90425</t>
+          <t>90132</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69163</t>
+          <t>67953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93943</t>
+          <t>92577</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114202</t>
+          <t>118007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172312</t>
+          <t>172866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88927</t>
+          <t>89220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135855</t>
+          <t>134501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88766</t>
+          <t>90132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113546</t>
+          <t>114756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189749</t>
+          <t>189195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>247859</t>
+          <t>244054</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
